--- a/themes/microloan.xlsx
+++ b/themes/microloan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Если у вас нет договора, то реквизиты можно узнать в приложении [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/). </t>
+          <t xml:space="preserve">    Если у вас нет договора, то реквизиты можно узнать в приложении [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/) </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>убраны двойные пробелы; добавлена точка в конце предложения</t>
+          <t>убраны двойные пробелы</t>
         </is>
       </c>
     </row>
@@ -725,181 +725,161 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Если ситуация не изменится, отправьте скриншот с ошибкой и описание проблемы на почтовый ящик info@uralsibfinance.ru </t>
+          <t>Incorrect: Если данные по займу отображаются некорректно, отправьте скриншот и описание проблемы через форму обратной связи в [личном кабинете](https://lk.uralsibfinance.ru) раздел «Вопрос – ответ» - «Форма обратной связи».</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Если ситуация не изменится, отправьте скриншот с ошибкой и описание проблемы на почтовый ящик info@uralsibfinance.ru. </t>
+          <t>Incorrect: Если данные по займу отображаются некорректно, отправьте скриншот и описание проблемы через форму обратной связи в [личном кабинете](https://lk.uralsibfinance.ru) раздел «Вопрос – ответ» — «Форма обратной связи».</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>дефис-разделитель перед «Форма обратной связи» заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Incorrect: Если данные по займу отображаются некорректно, отправьте скриншот и описание проблемы через форму обратной связи в [личном кабинете](https://lk.uralsibfinance.ru) раздел «Вопрос – ответ» - «Форма обратной связи».</t>
+          <t xml:space="preserve">  · Воспользоваться другим браузером (Яндекс, Google).</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Incorrect: Если данные по займу отображаются некорректно, отправьте скриншот и описание проблемы через форму обратной связи в [личном кабинете](https://lk.uralsibfinance.ru) раздел «Вопрос – ответ» — «Форма обратной связи».</t>
+          <t xml:space="preserve">  · Воспользуйтесь другим браузером (Яндекс, Google).</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>дефис-разделитель перед «Форма обратной связи» заменён на тире</t>
+          <t>«Воспользоваться» (инфинитив) исправлено на «Воспользуйтесь» (повелительное наклонение) — согласование с однородными «Отключите», «Почистите»</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Воспользоваться другим браузером (Яндекс, Google).</t>
+          <t xml:space="preserve">  Если ситуация не изменится, отправьте скриншот с ошибкой и описание проблемы на почтовый ящик info@uralsibfinance.ru .</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Воспользуйтесь другим браузером (Яндекс, Google).</t>
+          <t xml:space="preserve">  Если ситуация не изменится, отправьте скриншот с ошибкой и описание проблемы на почтовый ящик info@uralsibfinance.ru.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>«Воспользоваться» (инфинитив) исправлено на «Воспользуйтесь» (повелительное наклонение) — согласование с однородными «Отключите», «Почистите»</t>
+          <t>убран лишний пробел перед точкой</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Если ситуация не изменится, отправьте скриншот с ошибкой и описание проблемы на почтовый ящик info@uralsibfinance.ru .</t>
+          <t xml:space="preserve">  · Скачать их в [личном кабинете](https://lk.uralsibfinance.ru) в разделе «Главная» - «Документы и информация по займам»</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Если ситуация не изменится, отправьте скриншот с ошибкой и описание проблемы на почтовый ящик info@uralsibfinance.ru.</t>
+          <t xml:space="preserve">  · Скачать их в [личном кабинете](https://lk.uralsibfinance.ru) в разделе «Главная» — «Документы и информация по займам»</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>убран лишний пробел перед точкой</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Скачать их в [личном кабинете](https://lk.uralsibfinance.ru) в разделе «Главная» - «Документы и информация по займам»</t>
+          <t xml:space="preserve">      Для уточнения информации напишите в чат приложения  [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Скачать их в [личном кабинете](https://lk.uralsibfinance.ru) в разделе «Главная» — «Документы и информация по займам»</t>
+          <t xml:space="preserve">      Для уточнения информации напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>дефис заменён на тире</t>
+          <t>убран двойной пробел</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Для уточнения информации напишите в чат приложения  [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)</t>
+          <t xml:space="preserve">      Для уточнения информации по статусу рассмотрения заявки, напишите в чат приложения  [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Для уточнения информации напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/).</t>
+          <t xml:space="preserve">      Для уточнения информации по статусу рассмотрения заявки, напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>убран двойной пробел; добавлена точка в конце предложения</t>
+          <t>убран двойной пробел</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Для уточнения информации по статусу рассмотрения заявки, напишите в чат приложения  [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)</t>
+          <t xml:space="preserve">     Оставайтесь на линии - сейчас соединю вас с оператором для уточнения статуса рассмотрения заявки по займу. </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Для уточнения информации по статусу рассмотрения заявки, напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/).</t>
+          <t xml:space="preserve">     Оставайтесь на линии — сейчас соединю вас с оператором для уточнения статуса рассмотрения заявки по займу. </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>убран двойной пробел; добавлена точка в конце предложения</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Оставайтесь на линии - сейчас соединю вас с оператором для уточнения статуса рассмотрения заявки по займу. </t>
+          <t xml:space="preserve">      Для закрытия заявки по займу, напишите в чат приложения  [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Оставайтесь на линии — сейчас соединю вас с оператором для уточнения статуса рассмотрения заявки по займу. </t>
+          <t xml:space="preserve">      Для закрытия заявки по займу, напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>дефис заменён на тире</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>283</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Для закрытия заявки по займу, напишите в чат приложения  [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Для закрытия заявки по займу, напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru).</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>убран двойной пробел; добавлена точка в конце предложения</t>
+          <t>убран двойной пробел</t>
         </is>
       </c>
     </row>
